--- a/resumo_executivo_terca.xlsx
+++ b/resumo_executivo_terca.xlsx
@@ -458,8 +458,10 @@
       <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
-        <v>23.70689655172414</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>23.71%</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -477,8 +479,10 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
-        <v>5.172413793103448</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5.17%</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -496,8 +500,10 @@
       <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>40.94827586206897</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>40.95%</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -515,8 +521,10 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
-        <v>30.17241379310345</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30.17%</t>
+        </is>
       </c>
     </row>
   </sheetData>
